--- a/results/江苏政策约束对照/江苏政策约束与历史趋势对照.xlsx
+++ b/results/江苏政策约束对照/江苏政策约束与历史趋势对照.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="372" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="496" uniqueCount="84">
   <si>
     <t>情景</t>
   </si>
@@ -256,6 +256,18 @@
   </si>
   <si>
     <t>ed265dca9237cf0917545370a4badcf21e43cddba4f8f1d5d7e53b88ffc70407</t>
+  </si>
+  <si>
+    <t>同一已训练正则BP集成、同一2023锚点</t>
+  </si>
+  <si>
+    <t>65c2a4a35145dc61c696cc4722b0a73292538332019f99ac13aee4ad764a07e5</t>
+  </si>
+  <si>
+    <t>07_BP_Ensemble/results/result.mat</t>
+  </si>
+  <si>
+    <t>/Users/cyt/Desktop/zby模型/PSO-BP/data/需水预测模型对照.xlsx</t>
   </si>
 </sst>
 </file>
@@ -304,16 +316,16 @@
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" customWidth="true"/>
-    <col min="2" max="2" width="24.42578125" customWidth="true"/>
-    <col min="3" max="3" width="24.42578125" customWidth="true"/>
-    <col min="4" max="4" width="24.42578125" customWidth="true"/>
-    <col min="5" max="5" width="35.28515625" customWidth="true"/>
-    <col min="6" max="6" width="18.85546875" customWidth="true"/>
-    <col min="7" max="7" width="18.85546875" customWidth="true"/>
-    <col min="8" max="8" width="21.140625" customWidth="true"/>
-    <col min="9" max="9" width="25.7109375" customWidth="true"/>
-    <col min="10" max="10" width="21.140625" customWidth="true"/>
+    <col min="1" max="1" width="5.28515625" customWidth="true"/>
+    <col min="2" max="2" width="14.7109375" customWidth="true"/>
+    <col min="3" max="3" width="14.7109375" customWidth="true"/>
+    <col min="4" max="4" width="14.7109375" customWidth="true"/>
+    <col min="5" max="5" width="21.7109375" customWidth="true"/>
+    <col min="6" max="6" width="11.7109375" customWidth="true"/>
+    <col min="7" max="7" width="11.7109375" customWidth="true"/>
+    <col min="8" max="8" width="12.7109375" customWidth="true"/>
+    <col min="9" max="9" width="14.7109375" customWidth="true"/>
+    <col min="10" max="10" width="12.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -353,16 +365,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>160.47624776067758</v>
+        <v>162.59936305964357</v>
       </c>
       <c r="C2" s="0">
-        <v>159.86630999764796</v>
+        <v>162.1450792561815</v>
       </c>
       <c r="D2" s="0">
-        <v>0.60993776302962033</v>
+        <v>0.45428380346206154</v>
       </c>
       <c r="E2" s="0">
-        <v>2.8719791453837615</v>
+        <v>2.0037020142051745</v>
       </c>
       <c r="F2" s="0">
         <v>363.72753364033997</v>
@@ -371,10 +383,10 @@
         <v>348.53459610341315</v>
       </c>
       <c r="H2" s="0">
-        <v>3.0971752971880306</v>
+        <v>3.0971752971880293</v>
       </c>
       <c r="I2" s="0">
-        <v>3.727266664050533</v>
+        <v>3.7272666640505312</v>
       </c>
       <c r="J2" s="0">
         <v>9.1404590387006568</v>
@@ -385,16 +397,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>160.90182214632344</v>
+        <v>162.77836104508094</v>
       </c>
       <c r="C3" s="0">
-        <v>160.11176595929626</v>
+        <v>162.20666765288874</v>
       </c>
       <c r="D3" s="0">
-        <v>0.79005618702717584</v>
+        <v>0.57169339219220205</v>
       </c>
       <c r="E3" s="0">
-        <v>3.6711331325008132</v>
+        <v>2.5041472507766684</v>
       </c>
       <c r="F3" s="0">
         <v>367.44943282214786</v>
@@ -403,10 +415,10 @@
         <v>348.53459610341315</v>
       </c>
       <c r="H3" s="0">
-        <v>3.5395360290126079</v>
+        <v>3.5395360290126066</v>
       </c>
       <c r="I3" s="0">
-        <v>4.2596215522971592</v>
+        <v>4.2596215522971574</v>
       </c>
       <c r="J3" s="0">
         <v>9.1404590387006568</v>
@@ -417,16 +429,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>162.02976617739264</v>
+        <v>163.54829125244339</v>
       </c>
       <c r="C4" s="0">
-        <v>160.97853848261698</v>
+        <v>162.82472202834637</v>
       </c>
       <c r="D4" s="0">
-        <v>1.0512276947756618</v>
+        <v>0.72356922409701951</v>
       </c>
       <c r="E4" s="0">
-        <v>4.7140279025518339</v>
+        <v>3.1046990899156981</v>
       </c>
       <c r="F4" s="0">
         <v>371.20941692257844</v>
@@ -435,10 +447,10 @@
         <v>348.53459610341315</v>
       </c>
       <c r="H4" s="0">
-        <v>4.0450778850176734</v>
+        <v>4.0450778850176716</v>
       </c>
       <c r="I4" s="0">
-        <v>4.868011173924546</v>
+        <v>4.8680111739245433</v>
       </c>
       <c r="J4" s="0">
         <v>9.1404590387006568</v>
@@ -449,16 +461,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>161.36031959941786</v>
+        <v>163.20348132848176</v>
       </c>
       <c r="C5" s="0">
-        <v>160.53158967260006</v>
+        <v>162.61272343277821</v>
       </c>
       <c r="D5" s="0">
-        <v>0.82872992681780033</v>
+        <v>0.59075789570354686</v>
       </c>
       <c r="E5" s="0">
-        <v>3.7632306510465696</v>
+        <v>2.5484737492878082</v>
       </c>
       <c r="F5" s="0">
         <v>367.44943282214786</v>
@@ -467,10 +479,10 @@
         <v>348.53459610341315</v>
       </c>
       <c r="H5" s="0">
-        <v>3.5395360290126074</v>
+        <v>3.5395360290126066</v>
       </c>
       <c r="I5" s="0">
-        <v>4.2596215522971583</v>
+        <v>4.2596215522971574</v>
       </c>
       <c r="J5" s="0">
         <v>9.1404590387006568</v>
@@ -481,16 +493,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>160.11236782285121</v>
+        <v>162.22283681275971</v>
       </c>
       <c r="C6" s="0">
-        <v>159.5283138507497</v>
+        <v>161.78280304265581</v>
       </c>
       <c r="D6" s="0">
-        <v>0.58405397210151477</v>
+        <v>0.44003377010389499</v>
       </c>
       <c r="E6" s="0">
-        <v>2.795107804821896</v>
+        <v>1.9626761662022716</v>
       </c>
       <c r="F6" s="0">
         <v>363.72753364033997</v>
@@ -499,10 +511,10 @@
         <v>348.53459610341315</v>
       </c>
       <c r="H6" s="0">
-        <v>3.0971752971880306</v>
+        <v>3.0971752971880289</v>
       </c>
       <c r="I6" s="0">
-        <v>3.727266664050533</v>
+        <v>3.7272666640505308</v>
       </c>
       <c r="J6" s="0">
         <v>9.1404590387006568</v>
@@ -517,22 +529,22 @@
   <dimension ref="A1:P36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" customWidth="true"/>
-    <col min="2" max="2" width="5.7109375" customWidth="true"/>
-    <col min="3" max="3" width="27.28515625" customWidth="true"/>
-    <col min="4" max="4" width="27.28515625" customWidth="true"/>
-    <col min="5" max="5" width="20.42578125" customWidth="true"/>
-    <col min="6" max="6" width="14.85546875" customWidth="true"/>
-    <col min="7" max="7" width="14.85546875" customWidth="true"/>
-    <col min="8" max="8" width="14.85546875" customWidth="true"/>
-    <col min="9" max="9" width="19.42578125" customWidth="true"/>
-    <col min="10" max="10" width="21.140625" customWidth="true"/>
-    <col min="11" max="11" width="21.140625" customWidth="true"/>
-    <col min="12" max="12" width="25.7109375" customWidth="true"/>
-    <col min="13" max="13" width="25.7109375" customWidth="true"/>
-    <col min="14" max="14" width="20.5703125" customWidth="true"/>
-    <col min="15" max="15" width="14.85546875" customWidth="true"/>
-    <col min="16" max="16" width="19.42578125" customWidth="true"/>
+    <col min="1" max="1" width="5.28515625" customWidth="true"/>
+    <col min="2" max="2" width="5.140625" customWidth="true"/>
+    <col min="3" max="3" width="13.7109375" customWidth="true"/>
+    <col min="4" max="4" width="13.7109375" customWidth="true"/>
+    <col min="5" max="5" width="13.7109375" customWidth="true"/>
+    <col min="6" max="6" width="11.7109375" customWidth="true"/>
+    <col min="7" max="7" width="11.7109375" customWidth="true"/>
+    <col min="8" max="8" width="11.7109375" customWidth="true"/>
+    <col min="9" max="9" width="12.7109375" customWidth="true"/>
+    <col min="10" max="10" width="12.7109375" customWidth="true"/>
+    <col min="11" max="11" width="12.7109375" customWidth="true"/>
+    <col min="12" max="12" width="14.7109375" customWidth="true"/>
+    <col min="13" max="13" width="14.7109375" customWidth="true"/>
+    <col min="14" max="14" width="14.7109375" customWidth="true"/>
+    <col min="15" max="15" width="7.7109375" customWidth="true"/>
+    <col min="16" max="16" width="9.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -593,13 +605,13 @@
         <v>2024</v>
       </c>
       <c r="C2" s="0">
-        <v>163.99839302317517</v>
+        <v>164.4748707566232</v>
       </c>
       <c r="D2" s="0">
-        <v>163.85406326546993</v>
+        <v>164.38619132866143</v>
       </c>
       <c r="E2" s="0">
-        <v>0.14432975770523626</v>
+        <v>0.088679427961778856</v>
       </c>
       <c r="F2" s="0">
         <v>383.27882359902429</v>
@@ -643,13 +655,13 @@
         <v>2025</v>
       </c>
       <c r="C3" s="0">
-        <v>163.09019176160828</v>
+        <v>163.97336291396618</v>
       </c>
       <c r="D3" s="0">
-        <v>162.8283501547069</v>
+        <v>163.8065671907485</v>
       </c>
       <c r="E3" s="0">
-        <v>0.26184160690138469</v>
+        <v>0.16679572321768887</v>
       </c>
       <c r="F3" s="0">
         <v>379.94877650284349</v>
@@ -693,13 +705,13 @@
         <v>2026</v>
       </c>
       <c r="C4" s="0">
-        <v>162.3270554917481</v>
+        <v>163.55132054552689</v>
       </c>
       <c r="D4" s="0">
-        <v>161.96962191238438</v>
+        <v>163.31537043441048</v>
       </c>
       <c r="E4" s="0">
-        <v>0.35743357936371467</v>
+        <v>0.23595011111640929</v>
       </c>
       <c r="F4" s="0">
         <v>376.64766190431192</v>
@@ -714,16 +726,16 @@
         <v>0.65114285714285713</v>
       </c>
       <c r="J4" s="0">
-        <v>4.8950400129231344</v>
+        <v>4.8950400129231326</v>
       </c>
       <c r="K4" s="0">
-        <v>4.8950400129231344</v>
+        <v>4.8950400129231326</v>
       </c>
       <c r="L4" s="0">
         <v>7.7836942660517501</v>
       </c>
       <c r="M4" s="0">
-        <v>5.8908901526907087</v>
+        <v>5.8908901526907069</v>
       </c>
       <c r="N4" s="0">
         <v>11</v>
@@ -743,13 +755,13 @@
         <v>2027</v>
       </c>
       <c r="C5" s="0">
-        <v>161.70558677798047</v>
+        <v>163.21259564728874</v>
       </c>
       <c r="D5" s="0">
-        <v>161.2692807100365</v>
+        <v>162.91468122506885</v>
       </c>
       <c r="E5" s="0">
-        <v>0.43630606794397409</v>
+        <v>0.29791442221988973</v>
       </c>
       <c r="F5" s="0">
         <v>373.37522842878053</v>
@@ -764,16 +776,16 @@
         <v>0.66085714285714281</v>
       </c>
       <c r="J5" s="0">
-        <v>4.3657476740084391</v>
+        <v>4.3657476740084382</v>
       </c>
       <c r="K5" s="0">
-        <v>4.3657476740084391</v>
+        <v>4.3657476740084382</v>
       </c>
       <c r="L5" s="0">
         <v>8.1027292711261811</v>
       </c>
       <c r="M5" s="0">
-        <v>5.2539182343865605</v>
+        <v>5.2539182343865596</v>
       </c>
       <c r="N5" s="0">
         <v>11</v>
@@ -793,13 +805,13 @@
         <v>2028</v>
       </c>
       <c r="C6" s="0">
-        <v>161.20188698298651</v>
+        <v>162.94645336639954</v>
       </c>
       <c r="D6" s="0">
-        <v>160.6993165612345</v>
+        <v>162.59229900031775</v>
       </c>
       <c r="E6" s="0">
-        <v>0.5025704217520115</v>
+        <v>0.35415436608178652</v>
       </c>
       <c r="F6" s="0">
         <v>370.13122688562231</v>
@@ -814,16 +826,16 @@
         <v>0.67057142857142849</v>
       </c>
       <c r="J6" s="0">
-        <v>3.8936868141611636</v>
+        <v>3.8936868141611618</v>
       </c>
       <c r="K6" s="0">
-        <v>3.8936868141611636</v>
+        <v>3.8936868141611618</v>
       </c>
       <c r="L6" s="0">
         <v>8.4348407577508659</v>
       </c>
       <c r="M6" s="0">
-        <v>4.6858210046594433</v>
+        <v>4.6858210046594415</v>
       </c>
       <c r="N6" s="0">
         <v>11</v>
@@ -843,13 +855,13 @@
         <v>2029</v>
       </c>
       <c r="C7" s="0">
-        <v>160.79708645206475</v>
+        <v>162.74433075594325</v>
       </c>
       <c r="D7" s="0">
-        <v>160.23752650337693</v>
+        <v>162.33840659579769</v>
       </c>
       <c r="E7" s="0">
-        <v>0.55955994868782</v>
+        <v>0.40592416014555965</v>
       </c>
       <c r="F7" s="0">
         <v>366.91541024925692</v>
@@ -864,16 +876,16 @@
         <v>0.68028571428571427</v>
       </c>
       <c r="J7" s="0">
-        <v>3.4726690910316687</v>
+        <v>3.4726690910316678</v>
       </c>
       <c r="K7" s="0">
-        <v>3.4726690910316687</v>
+        <v>3.4726690910316678</v>
       </c>
       <c r="L7" s="0">
         <v>8.7805646996183899</v>
       </c>
       <c r="M7" s="0">
-        <v>4.1791511607472298</v>
+        <v>4.1791511607472289</v>
       </c>
       <c r="N7" s="0">
         <v>11</v>
@@ -893,13 +905,13 @@
         <v>2030</v>
       </c>
       <c r="C8" s="0">
-        <v>160.47624776067758</v>
+        <v>162.59936305964357</v>
       </c>
       <c r="D8" s="0">
-        <v>159.86630999764796</v>
+        <v>162.1450792561815</v>
       </c>
       <c r="E8" s="0">
-        <v>0.60993776302962033</v>
+        <v>0.45428380346206154</v>
       </c>
       <c r="F8" s="0">
         <v>363.72753364033997</v>
@@ -914,16 +926,16 @@
         <v>0.68999999999999995</v>
       </c>
       <c r="J8" s="0">
-        <v>3.0971752971880306</v>
+        <v>3.0971752971880293</v>
       </c>
       <c r="K8" s="0">
-        <v>3.0971752971880306</v>
+        <v>3.0971752971880293</v>
       </c>
       <c r="L8" s="0">
         <v>9.1404590387006568</v>
       </c>
       <c r="M8" s="0">
-        <v>3.727266664050533</v>
+        <v>3.7272666640505312</v>
       </c>
       <c r="N8" s="0">
         <v>11</v>
@@ -943,13 +955,13 @@
         <v>2024</v>
       </c>
       <c r="C9" s="0">
-        <v>164.18379307645469</v>
+        <v>164.56953805219825</v>
       </c>
       <c r="D9" s="0">
-        <v>164.00633531655618</v>
+        <v>164.46117903195341</v>
       </c>
       <c r="E9" s="0">
-        <v>0.17745775989851609</v>
+        <v>0.10835902024484767</v>
       </c>
       <c r="F9" s="0">
         <v>383.83666210292881</v>
@@ -993,13 +1005,13 @@
         <v>2025</v>
       </c>
       <c r="C10" s="0">
-        <v>163.4053903801022</v>
+        <v>164.13567579262497</v>
       </c>
       <c r="D10" s="0">
-        <v>163.07886598959433</v>
+        <v>163.93019403217457</v>
       </c>
       <c r="E10" s="0">
-        <v>0.32652439050787052</v>
+        <v>0.20548176045039668</v>
       </c>
       <c r="F10" s="0">
         <v>381.05556500276555</v>
@@ -1014,16 +1026,16 @@
         <v>0.64142857142857146</v>
       </c>
       <c r="J10" s="0">
-        <v>5.7019017889405408</v>
+        <v>5.7019017889405399</v>
       </c>
       <c r="K10" s="0">
-        <v>5.7019017889405408</v>
+        <v>5.7019017889405399</v>
       </c>
       <c r="L10" s="0">
         <v>7.4772208721403066</v>
       </c>
       <c r="M10" s="0">
-        <v>6.8619004158090853</v>
+        <v>6.8619004158090844</v>
       </c>
       <c r="N10" s="0">
         <v>11</v>
@@ -1043,13 +1055,13 @@
         <v>2026</v>
       </c>
       <c r="C11" s="0">
-        <v>162.72588219412901</v>
+        <v>163.75690974914644</v>
       </c>
       <c r="D11" s="0">
-        <v>162.27457611763217</v>
+        <v>163.46416615192814</v>
       </c>
       <c r="E11" s="0">
-        <v>0.45130607649684862</v>
+        <v>0.29274359721830479</v>
       </c>
       <c r="F11" s="0">
         <v>378.29461840369868</v>
@@ -1064,16 +1076,16 @@
         <v>0.65114285714285713</v>
       </c>
       <c r="J11" s="0">
-        <v>5.1832845781137689</v>
+        <v>5.183284578113768</v>
       </c>
       <c r="K11" s="0">
-        <v>5.1832845781137689</v>
+        <v>5.183284578113768</v>
       </c>
       <c r="L11" s="0">
         <v>7.7836942660517501</v>
       </c>
       <c r="M11" s="0">
-        <v>6.2377753806286371</v>
+        <v>6.2377753806286362</v>
       </c>
       <c r="N11" s="0">
         <v>11</v>
@@ -1093,13 +1105,13 @@
         <v>2027</v>
       </c>
       <c r="C12" s="0">
-        <v>162.15134666554846</v>
+        <v>163.43991055875333</v>
       </c>
       <c r="D12" s="0">
-        <v>161.59477054668199</v>
+        <v>163.06813799635407</v>
       </c>
       <c r="E12" s="0">
-        <v>0.55657611886647373</v>
+        <v>0.37177256239925782</v>
       </c>
       <c r="F12" s="0">
         <v>375.55367630482277</v>
@@ -1114,16 +1126,16 @@
         <v>0.66085714285714281</v>
       </c>
       <c r="J12" s="0">
-        <v>4.7118382624236723</v>
+        <v>4.7118382624236714</v>
       </c>
       <c r="K12" s="0">
-        <v>4.7118382624236723</v>
+        <v>4.7118382624236714</v>
       </c>
       <c r="L12" s="0">
         <v>8.1027292711261811</v>
       </c>
       <c r="M12" s="0">
-        <v>5.6704177183237192</v>
+        <v>5.6704177183237183</v>
       </c>
       <c r="N12" s="0">
         <v>11</v>
@@ -1143,13 +1155,13 @@
         <v>2028</v>
       </c>
       <c r="C13" s="0">
-        <v>161.66463170721639</v>
+        <v>163.17580300969129</v>
       </c>
       <c r="D13" s="0">
-        <v>161.01850984113062</v>
+        <v>162.73191661247611</v>
       </c>
       <c r="E13" s="0">
-        <v>0.64612186608576394</v>
+        <v>0.44388639721518075</v>
       </c>
       <c r="F13" s="0">
         <v>372.83259376308547</v>
@@ -1164,16 +1176,16 @@
         <v>0.67057142857142849</v>
       </c>
       <c r="J13" s="0">
-        <v>4.2832724070340307</v>
+        <v>4.2832724070340298</v>
       </c>
       <c r="K13" s="0">
-        <v>4.2832724070340307</v>
+        <v>4.2832724070340298</v>
       </c>
       <c r="L13" s="0">
         <v>8.4348407577508659</v>
       </c>
       <c r="M13" s="0">
-        <v>5.1546641451906794</v>
+        <v>5.1546641451906785</v>
       </c>
       <c r="N13" s="0">
         <v>11</v>
@@ -1193,13 +1205,13 @@
         <v>2029</v>
       </c>
       <c r="C14" s="0">
-        <v>161.25189407419217</v>
+        <v>162.9573087336141</v>
       </c>
       <c r="D14" s="0">
-        <v>160.528803340574</v>
+        <v>162.44709821255762</v>
       </c>
       <c r="E14" s="0">
-        <v>0.72309073361816445</v>
+        <v>0.51021052105647868</v>
       </c>
       <c r="F14" s="0">
         <v>370.13122688562231</v>
@@ -1214,16 +1226,16 @@
         <v>0.68028571428571427</v>
       </c>
       <c r="J14" s="0">
-        <v>3.8936868141611636</v>
+        <v>3.8936868141611618</v>
       </c>
       <c r="K14" s="0">
-        <v>3.8936868141611636</v>
+        <v>3.8936868141611618</v>
       </c>
       <c r="L14" s="0">
         <v>8.7805646996183899</v>
       </c>
       <c r="M14" s="0">
-        <v>4.6858210046594433</v>
+        <v>4.6858210046594415</v>
       </c>
       <c r="N14" s="0">
         <v>11</v>
@@ -1243,13 +1255,13 @@
         <v>2030</v>
       </c>
       <c r="C15" s="0">
-        <v>160.90182214632344</v>
+        <v>162.77836104508094</v>
       </c>
       <c r="D15" s="0">
-        <v>160.11176595929626</v>
+        <v>162.20666765288874</v>
       </c>
       <c r="E15" s="0">
-        <v>0.79005618702717584</v>
+        <v>0.57169339219220205</v>
       </c>
       <c r="F15" s="0">
         <v>367.44943282214786</v>
@@ -1264,16 +1276,16 @@
         <v>0.68999999999999995</v>
       </c>
       <c r="J15" s="0">
-        <v>3.5395360290126079</v>
+        <v>3.5395360290126066</v>
       </c>
       <c r="K15" s="0">
-        <v>3.5395360290126079</v>
+        <v>3.5395360290126066</v>
       </c>
       <c r="L15" s="0">
         <v>9.1404590387006568</v>
       </c>
       <c r="M15" s="0">
-        <v>4.2596215522971592</v>
+        <v>4.2596215522971574</v>
       </c>
       <c r="N15" s="0">
         <v>11</v>
@@ -1293,13 +1305,13 @@
         <v>2024</v>
       </c>
       <c r="C16" s="0">
-        <v>164.38572511983219</v>
+        <v>164.67302725600658</v>
       </c>
       <c r="D16" s="0">
-        <v>164.17419625519531</v>
+        <v>164.54470676967648</v>
       </c>
       <c r="E16" s="0">
-        <v>0.21152886463687537</v>
+        <v>0.12832048633009663</v>
       </c>
       <c r="F16" s="0">
         <v>384.39531250610167</v>
@@ -1343,13 +1355,13 @@
         <v>2025</v>
       </c>
       <c r="C17" s="0">
-        <v>163.87658220774838</v>
+        <v>164.41462707096798</v>
       </c>
       <c r="D17" s="0">
-        <v>163.4786063067593</v>
+        <v>164.16796436844359</v>
       </c>
       <c r="E17" s="0">
-        <v>0.39797590098908131</v>
+        <v>0.24666270252438949</v>
       </c>
       <c r="F17" s="0">
         <v>382.16557757092869</v>
@@ -1393,13 +1405,13 @@
         <v>2026</v>
       </c>
       <c r="C18" s="0">
-        <v>163.40979425302626</v>
+        <v>164.18191529280378</v>
       </c>
       <c r="D18" s="0">
-        <v>162.84791015287615</v>
+        <v>163.82594933505655</v>
       </c>
       <c r="E18" s="0">
-        <v>0.56188410015010959</v>
+        <v>0.35596595774723028</v>
       </c>
       <c r="F18" s="0">
         <v>379.94877650284349</v>
@@ -1443,13 +1455,13 @@
         <v>2027</v>
       </c>
       <c r="C19" s="0">
-        <v>163.00089739771525</v>
+        <v>163.98491070706658</v>
       </c>
       <c r="D19" s="0">
-        <v>162.29414174057209</v>
+        <v>163.52743712330894</v>
       </c>
       <c r="E19" s="0">
-        <v>0.70675565714316235</v>
+        <v>0.4574735837576327</v>
       </c>
       <c r="F19" s="0">
         <v>377.74483427727017</v>
@@ -1464,16 +1476,16 @@
         <v>0.66085714285714281</v>
       </c>
       <c r="J19" s="0">
-        <v>5.0853648605063242</v>
+        <v>5.0853648605063224</v>
       </c>
       <c r="K19" s="0">
-        <v>5.0853648605063242</v>
+        <v>5.0853648605063224</v>
       </c>
       <c r="L19" s="0">
         <v>8.1027292711261811</v>
       </c>
       <c r="M19" s="0">
-        <v>6.1199348116679992</v>
+        <v>6.1199348116679975</v>
       </c>
       <c r="N19" s="0">
         <v>11</v>
@@ -1493,13 +1505,13 @@
         <v>2028</v>
       </c>
       <c r="C20" s="0">
-        <v>162.63981450498679</v>
+        <v>163.81713336301104</v>
       </c>
       <c r="D20" s="0">
-        <v>161.80460015589509</v>
+        <v>163.26502966281927</v>
       </c>
       <c r="E20" s="0">
-        <v>0.83521434909170011</v>
+        <v>0.5521037001917648</v>
       </c>
       <c r="F20" s="0">
         <v>375.55367630482277</v>
@@ -1514,16 +1526,16 @@
         <v>0.67057142857142849</v>
       </c>
       <c r="J20" s="0">
-        <v>4.7118382624236723</v>
+        <v>4.7118382624236714</v>
       </c>
       <c r="K20" s="0">
-        <v>4.7118382624236723</v>
+        <v>4.7118382624236714</v>
       </c>
       <c r="L20" s="0">
         <v>8.4348407577508659</v>
       </c>
       <c r="M20" s="0">
-        <v>5.6704177183237192</v>
+        <v>5.6704177183237183</v>
       </c>
       <c r="N20" s="0">
         <v>11</v>
@@ -1543,13 +1555,13 @@
         <v>2029</v>
       </c>
       <c r="C21" s="0">
-        <v>162.31837461316277</v>
+        <v>163.673153193015</v>
       </c>
       <c r="D21" s="0">
-        <v>161.36893327739753</v>
+        <v>163.03254975774743</v>
       </c>
       <c r="E21" s="0">
-        <v>0.94944133576524337</v>
+        <v>0.64060343526756469</v>
       </c>
       <c r="F21" s="0">
         <v>373.37522842878053</v>
@@ -1564,16 +1576,16 @@
         <v>0.68028571428571427</v>
       </c>
       <c r="J21" s="0">
-        <v>4.3657476740084391</v>
+        <v>4.3657476740084382</v>
       </c>
       <c r="K21" s="0">
-        <v>4.3657476740084391</v>
+        <v>4.3657476740084382</v>
       </c>
       <c r="L21" s="0">
         <v>8.7805646996183899</v>
       </c>
       <c r="M21" s="0">
-        <v>5.2539182343865605</v>
+        <v>5.2539182343865596</v>
       </c>
       <c r="N21" s="0">
         <v>11</v>
@@ -1593,13 +1605,13 @@
         <v>2030</v>
       </c>
       <c r="C22" s="0">
-        <v>162.02976617739264</v>
+        <v>163.54829125244339</v>
       </c>
       <c r="D22" s="0">
-        <v>160.97853848261698</v>
+        <v>162.82472202834637</v>
       </c>
       <c r="E22" s="0">
-        <v>1.0512276947756618</v>
+        <v>0.72356922409701951</v>
       </c>
       <c r="F22" s="0">
         <v>371.20941692257844</v>
@@ -1614,16 +1626,16 @@
         <v>0.68999999999999995</v>
       </c>
       <c r="J22" s="0">
-        <v>4.0450778850176734</v>
+        <v>4.0450778850176716</v>
       </c>
       <c r="K22" s="0">
-        <v>4.0450778850176734</v>
+        <v>4.0450778850176716</v>
       </c>
       <c r="L22" s="0">
         <v>9.1404590387006568</v>
       </c>
       <c r="M22" s="0">
-        <v>4.868011173924546</v>
+        <v>4.8680111739245433</v>
       </c>
       <c r="N22" s="0">
         <v>11</v>
@@ -1643,13 +1655,13 @@
         <v>2024</v>
       </c>
       <c r="C23" s="0">
-        <v>164.19715386863348</v>
+        <v>164.57953360994256</v>
       </c>
       <c r="D23" s="0">
-        <v>164.01954217428639</v>
+        <v>164.47111208956099</v>
       </c>
       <c r="E23" s="0">
-        <v>0.17761169434709245</v>
+        <v>0.10842152038156883</v>
       </c>
       <c r="F23" s="0">
         <v>383.83666210292881</v>
@@ -1693,13 +1705,13 @@
         <v>2025</v>
       </c>
       <c r="C24" s="0">
-        <v>163.45244332370308</v>
+        <v>164.17326296256701</v>
       </c>
       <c r="D24" s="0">
-        <v>163.12480124154072</v>
+        <v>163.96729971165348</v>
       </c>
       <c r="E24" s="0">
-        <v>0.32764208216235602</v>
+        <v>0.20596325091352696</v>
       </c>
       <c r="F24" s="0">
         <v>381.05556500276555</v>
@@ -1743,13 +1755,13 @@
         <v>2026</v>
       </c>
       <c r="C25" s="0">
-        <v>162.82433517262714</v>
+        <v>163.8388305998279</v>
       </c>
       <c r="D25" s="0">
-        <v>162.36945431340601</v>
+        <v>163.54448971731844</v>
       </c>
       <c r="E25" s="0">
-        <v>0.45488085922113441</v>
+        <v>0.29434088250945933</v>
       </c>
       <c r="F25" s="0">
         <v>378.29461840369868</v>
@@ -1793,13 +1805,13 @@
         <v>2027</v>
       </c>
       <c r="C26" s="0">
-        <v>162.31735314661475</v>
+        <v>163.58262820418608</v>
       </c>
       <c r="D26" s="0">
-        <v>161.75266922070566</v>
+        <v>163.20712392957537</v>
       </c>
       <c r="E26" s="0">
-        <v>0.56468392590909389</v>
+        <v>0.37550427461070512</v>
       </c>
       <c r="F26" s="0">
         <v>375.55367630482277</v>
@@ -1814,16 +1826,16 @@
         <v>0.66085714285714281</v>
       </c>
       <c r="J26" s="0">
-        <v>4.7118382624236723</v>
+        <v>4.7118382624236714</v>
       </c>
       <c r="K26" s="0">
-        <v>4.7118382624236723</v>
+        <v>4.7118382624236714</v>
       </c>
       <c r="L26" s="0">
         <v>8.1027292711261811</v>
       </c>
       <c r="M26" s="0">
-        <v>5.6704177183237192</v>
+        <v>5.6704177183237183</v>
       </c>
       <c r="N26" s="0">
         <v>11</v>
@@ -1843,13 +1855,13 @@
         <v>2028</v>
       </c>
       <c r="C27" s="0">
-        <v>161.9133497845385</v>
+        <v>163.39575223633111</v>
       </c>
       <c r="D27" s="0">
-        <v>161.25202641548483</v>
+        <v>162.9446861805086</v>
       </c>
       <c r="E27" s="0">
-        <v>0.66132336905366174</v>
+        <v>0.45106605582250836</v>
       </c>
       <c r="F27" s="0">
         <v>372.83259376308547</v>
@@ -1864,16 +1876,16 @@
         <v>0.67057142857142849</v>
       </c>
       <c r="J27" s="0">
-        <v>4.2832724070340307</v>
+        <v>4.2832724070340298</v>
       </c>
       <c r="K27" s="0">
-        <v>4.2832724070340307</v>
+        <v>4.2832724070340298</v>
       </c>
       <c r="L27" s="0">
         <v>8.4348407577508659</v>
       </c>
       <c r="M27" s="0">
-        <v>5.1546641451906794</v>
+        <v>5.1546641451906785</v>
       </c>
       <c r="N27" s="0">
         <v>11</v>
@@ -1893,13 +1905,13 @@
         <v>2029</v>
       </c>
       <c r="C28" s="0">
-        <v>161.59807606035511</v>
+        <v>163.27120556907315</v>
       </c>
       <c r="D28" s="0">
-        <v>160.84971726681968</v>
+        <v>162.74878569972665</v>
       </c>
       <c r="E28" s="0">
-        <v>0.74835879353543078</v>
+        <v>0.52241986934649276</v>
       </c>
       <c r="F28" s="0">
         <v>370.13122688562231</v>
@@ -1914,16 +1926,16 @@
         <v>0.68028571428571427</v>
       </c>
       <c r="J28" s="0">
-        <v>3.8936868141611636</v>
+        <v>3.8936868141611618</v>
       </c>
       <c r="K28" s="0">
-        <v>3.8936868141611636</v>
+        <v>3.8936868141611618</v>
       </c>
       <c r="L28" s="0">
         <v>8.7805646996183899</v>
       </c>
       <c r="M28" s="0">
-        <v>4.6858210046594433</v>
+        <v>4.6858210046594415</v>
       </c>
       <c r="N28" s="0">
         <v>11</v>
@@ -1943,13 +1955,13 @@
         <v>2030</v>
       </c>
       <c r="C29" s="0">
-        <v>161.36031959941786</v>
+        <v>163.20348132848176</v>
       </c>
       <c r="D29" s="0">
-        <v>160.53158967260006</v>
+        <v>162.61272343277821</v>
       </c>
       <c r="E29" s="0">
-        <v>0.82872992681780033</v>
+        <v>0.59075789570354686</v>
       </c>
       <c r="F29" s="0">
         <v>367.44943282214786</v>
@@ -1964,16 +1976,16 @@
         <v>0.68999999999999995</v>
       </c>
       <c r="J29" s="0">
-        <v>3.5395360290126074</v>
+        <v>3.5395360290126066</v>
       </c>
       <c r="K29" s="0">
-        <v>3.5395360290126074</v>
+        <v>3.5395360290126066</v>
       </c>
       <c r="L29" s="0">
         <v>9.1404590387006568</v>
       </c>
       <c r="M29" s="0">
-        <v>4.2596215522971583</v>
+        <v>4.2596215522971574</v>
       </c>
       <c r="N29" s="0">
         <v>11</v>
@@ -1993,13 +2005,13 @@
         <v>2024</v>
       </c>
       <c r="C30" s="0">
-        <v>164.00777415165138</v>
+        <v>164.47896102783025</v>
       </c>
       <c r="D30" s="0">
-        <v>163.86335427922401</v>
+        <v>164.3902603462378</v>
       </c>
       <c r="E30" s="0">
-        <v>0.14441987242736332</v>
+        <v>0.088700681592456476</v>
       </c>
       <c r="F30" s="0">
         <v>383.27882359902429</v>
@@ -2014,16 +2026,16 @@
         <v>0.63171428571428567</v>
       </c>
       <c r="J30" s="0">
-        <v>6.1539147527150693</v>
+        <v>6.1539147527150675</v>
       </c>
       <c r="K30" s="0">
-        <v>6.1539147527150693</v>
+        <v>6.1539147527150675</v>
       </c>
       <c r="L30" s="0">
         <v>7.1828144913931986</v>
       </c>
       <c r="M30" s="0">
-        <v>7.405871192382536</v>
+        <v>7.4058711923825342</v>
       </c>
       <c r="N30" s="0">
         <v>11</v>
@@ -2043,13 +2055,13 @@
         <v>2025</v>
       </c>
       <c r="C31" s="0">
-        <v>163.00081331264951</v>
+        <v>163.89090552699315</v>
       </c>
       <c r="D31" s="0">
-        <v>162.74075710846049</v>
+        <v>163.72499472037973</v>
       </c>
       <c r="E31" s="0">
-        <v>0.26005620418902708</v>
+        <v>0.16591080661342517</v>
       </c>
       <c r="F31" s="0">
         <v>379.94877650284349</v>
@@ -2093,13 +2105,13 @@
         <v>2026</v>
       </c>
       <c r="C32" s="0">
-        <v>162.15952906176611</v>
+        <v>163.39477302566306</v>
       </c>
       <c r="D32" s="0">
-        <v>161.80723326207104</v>
+        <v>163.16139254018776</v>
       </c>
       <c r="E32" s="0">
-        <v>0.35229579969507085</v>
+        <v>0.23338048547529411</v>
       </c>
       <c r="F32" s="0">
         <v>376.64766190431192</v>
@@ -2114,16 +2126,16 @@
         <v>0.65114285714285713</v>
       </c>
       <c r="J32" s="0">
-        <v>4.8950400129231344</v>
+        <v>4.8950400129231326</v>
       </c>
       <c r="K32" s="0">
-        <v>4.8950400129231344</v>
+        <v>4.8950400129231326</v>
       </c>
       <c r="L32" s="0">
         <v>7.7836942660517501</v>
       </c>
       <c r="M32" s="0">
-        <v>5.8908901526907087</v>
+        <v>5.8908901526907069</v>
       </c>
       <c r="N32" s="0">
         <v>11</v>
@@ -2143,13 +2155,13 @@
         <v>2027</v>
       </c>
       <c r="C33" s="0">
-        <v>161.47534611740221</v>
+        <v>162.99175619689834</v>
       </c>
       <c r="D33" s="0">
-        <v>161.0485544338579</v>
+        <v>162.698715825823</v>
       </c>
       <c r="E33" s="0">
-        <v>0.42679168354430885</v>
+        <v>0.29304037107533532</v>
       </c>
       <c r="F33" s="0">
         <v>373.37522842878053</v>
@@ -2164,16 +2176,16 @@
         <v>0.66085714285714281</v>
       </c>
       <c r="J33" s="0">
-        <v>4.3657476740084391</v>
+        <v>4.3657476740084382</v>
       </c>
       <c r="K33" s="0">
-        <v>4.3657476740084391</v>
+        <v>4.3657476740084382</v>
       </c>
       <c r="L33" s="0">
         <v>8.1027292711261811</v>
       </c>
       <c r="M33" s="0">
-        <v>5.2539182343865605</v>
+        <v>5.2539182343865596</v>
       </c>
       <c r="N33" s="0">
         <v>11</v>
@@ -2193,13 +2205,13 @@
         <v>2028</v>
       </c>
       <c r="C34" s="0">
-        <v>160.9201428916347</v>
+        <v>162.66880106233478</v>
       </c>
       <c r="D34" s="0">
-        <v>160.43214181872602</v>
+        <v>162.32230473874094</v>
       </c>
       <c r="E34" s="0">
-        <v>0.48800107290867345</v>
+        <v>0.34649632359383986</v>
       </c>
       <c r="F34" s="0">
         <v>370.13122688562231</v>
@@ -2214,16 +2226,16 @@
         <v>0.67057142857142849</v>
       </c>
       <c r="J34" s="0">
-        <v>3.8936868141611631</v>
+        <v>3.8936868141611618</v>
       </c>
       <c r="K34" s="0">
-        <v>3.8936868141611631</v>
+        <v>3.8936868141611618</v>
       </c>
       <c r="L34" s="0">
         <v>8.4348407577508659</v>
       </c>
       <c r="M34" s="0">
-        <v>4.6858210046594424</v>
+        <v>4.6858210046594415</v>
       </c>
       <c r="N34" s="0">
         <v>11</v>
@@ -2243,13 +2255,13 @@
         <v>2029</v>
       </c>
       <c r="C35" s="0">
-        <v>160.47168462248843</v>
+        <v>162.41535206017434</v>
       </c>
       <c r="D35" s="0">
-        <v>159.93219542253249</v>
+        <v>162.02023833242632</v>
       </c>
       <c r="E35" s="0">
-        <v>0.53948919995593769</v>
+        <v>0.39511372774802567</v>
       </c>
       <c r="F35" s="0">
         <v>366.91541024925692</v>
@@ -2264,16 +2276,16 @@
         <v>0.68028571428571427</v>
       </c>
       <c r="J35" s="0">
-        <v>3.4726690910316682</v>
+        <v>3.4726690910316673</v>
       </c>
       <c r="K35" s="0">
-        <v>3.4726690910316682</v>
+        <v>3.4726690910316673</v>
       </c>
       <c r="L35" s="0">
         <v>8.7805646996183899</v>
       </c>
       <c r="M35" s="0">
-        <v>4.1791511607472289</v>
+        <v>4.179151160747228</v>
       </c>
       <c r="N35" s="0">
         <v>11</v>
@@ -2293,13 +2305,13 @@
         <v>2030</v>
       </c>
       <c r="C36" s="0">
-        <v>160.11236782285121</v>
+        <v>162.22283681275971</v>
       </c>
       <c r="D36" s="0">
-        <v>159.5283138507497</v>
+        <v>161.78280304265581</v>
       </c>
       <c r="E36" s="0">
-        <v>0.58405397210151477</v>
+        <v>0.44003377010389499</v>
       </c>
       <c r="F36" s="0">
         <v>363.72753364033997</v>
@@ -2314,16 +2326,16 @@
         <v>0.68999999999999995</v>
       </c>
       <c r="J36" s="0">
-        <v>3.0971752971880306</v>
+        <v>3.0971752971880289</v>
       </c>
       <c r="K36" s="0">
-        <v>3.0971752971880306</v>
+        <v>3.0971752971880289</v>
       </c>
       <c r="L36" s="0">
         <v>9.1404590387006568</v>
       </c>
       <c r="M36" s="0">
-        <v>3.727266664050533</v>
+        <v>3.7272666640505308</v>
       </c>
       <c r="N36" s="0">
         <v>11</v>
@@ -2344,10 +2356,10 @@
   <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="true"/>
-    <col min="2" max="2" width="64.5703125" customWidth="true"/>
-    <col min="3" max="3" width="88.85546875" customWidth="true"/>
-    <col min="4" max="4" width="157" customWidth="true"/>
+    <col min="1" max="1" width="16.7109375" customWidth="true"/>
+    <col min="2" max="2" width="64.85546875" customWidth="true"/>
+    <col min="3" max="3" width="43.7109375" customWidth="true"/>
+    <col min="4" max="4" width="112.140625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2537,13 +2549,13 @@
         <v>40</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>63</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15">
@@ -2551,13 +2563,13 @@
         <v>41</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>64</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -2583,8 +2595,8 @@
   <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" customWidth="true"/>
-    <col min="2" max="2" width="34.85546875" customWidth="true"/>
+    <col min="1" max="1" width="5.140625" customWidth="true"/>
+    <col min="2" max="2" width="18.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
